--- a/Result/profitability/8401.xlsx
+++ b/Result/profitability/8401.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.73875</v>
       </c>
       <c r="N2" t="n">
-        <v>30.0975</v>
+        <v>30.29875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.67125</v>
+        <v>0.64125</v>
       </c>
       <c r="N3" t="n">
-        <v>28.875</v>
+        <v>28.79</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6637500000000001</v>
+        <v>0.68625</v>
       </c>
       <c r="N4" t="n">
-        <v>28.22125</v>
+        <v>28.545</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.62375</v>
+        <v>0.61375</v>
       </c>
       <c r="N5" t="n">
-        <v>27.34625</v>
+        <v>27.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0.64625</v>
       </c>
       <c r="N6" t="n">
-        <v>27.11</v>
+        <v>27.19875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61</v>
+        <v>0.5737500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>26.2775</v>
+        <v>26.16125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0.64125</v>
+        <v>0.6625000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>25.3075</v>
+        <v>25.485</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0.65125</v>
+        <v>0.6512500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>24.6725</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8401</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>403</v>
+      </c>
+      <c r="D74" t="n">
+        <v>276</v>
+      </c>
+      <c r="E74" t="n">
+        <v>127</v>
+      </c>
+      <c r="F74" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="G74" t="n">
+        <v>56</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>13.95%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>55</v>
+      </c>
+      <c r="K74" t="n">
+        <v>44</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.6625000000000001</v>
+      </c>
+      <c r="N74" t="n">
+        <v>30.76625</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.3695652173913042</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.419999999999998</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.04711347047113468</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-0.1126760563380281</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.629999999999999</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.05446040761777482</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
